--- a/yanfeng/项目信息表/发运前检查计划.xlsx
+++ b/yanfeng/项目信息表/发运前检查计划.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,6 +487,142 @@
           <t>Phase 4 score</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>30033404</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>30033404-2026,AP,VW Group,VW426-DP,Lamination,260033,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Huang Linjian_黄琳健(uhual254)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>30033404</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>260033</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>VW Group,VW426-DP,Lamination</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>30035089</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>30035089-2026,AP,SAIC-GM,E2LB-2-IP, Automation, 260129, M,Equipment</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Zou Chengcheng_邹成成(uzouc016)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Wang Xiaoyu03_王晓宇(uwanx1357)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30035089</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>260129</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>SAIC-GM,E2LB-2-IP, Automation</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/yanfeng/项目信息表/发运前检查计划.xlsx
+++ b/yanfeng/项目信息表/发运前检查计划.xlsx
@@ -1,34 +1,112 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
+  <si>
+    <t>Project ID</t>
+  </si>
+  <si>
+    <t>Project Name</t>
+  </si>
+  <si>
+    <t>EBP Leader</t>
+  </si>
+  <si>
+    <t>Product Engineer</t>
+  </si>
+  <si>
+    <t>Project State</t>
+  </si>
+  <si>
+    <t>Phase 2 Gate Exit-DVR</t>
+  </si>
+  <si>
+    <t>Phase 3 Gate Exit-FPR</t>
+  </si>
+  <si>
+    <t>Phase 4 Gate Exit-CPA</t>
+  </si>
+  <si>
+    <t>项目号</t>
+  </si>
+  <si>
+    <t>工作令号</t>
+  </si>
+  <si>
+    <t>项目名</t>
+  </si>
+  <si>
+    <t>phase 2 score</t>
+  </si>
+  <si>
+    <t>phase 3 score</t>
+  </si>
+  <si>
+    <t>Phase 4 score</t>
+  </si>
+  <si>
+    <t>30034623</t>
+  </si>
+  <si>
+    <t>30034623-2026,AP,BYD,Glue,260103,M,Equipment</t>
+  </si>
+  <si>
+    <t>Shang Bing_尚兵(ushab007)</t>
+  </si>
+  <si>
+    <t>Chen Jie04_陈洁(uchej018)</t>
+  </si>
+  <si>
+    <t>Phase 4 Manufacturing Development</t>
+  </si>
+  <si>
+    <t>2026-05-22</t>
+  </si>
+  <si>
+    <t>2026-05-30</t>
+  </si>
+  <si>
+    <t>2026-06-20</t>
+  </si>
+  <si>
+    <t>260103</t>
+  </si>
+  <si>
+    <t>BYD,Glue</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +125,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -408,223 +419,96 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Project ID</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Project Name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>EBP Leader</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Product Engineer</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Project State</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Phase 2 Gate Exit-DVR</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Phase 3 Gate Exit-FPR</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Phase 4 Gate Exit-CPA</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>项目号</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>工作令号</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>项目名</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>phase 2 score</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>phase 3 score</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Phase 4 score</t>
-        </is>
+    <row r="1" spans="1:14">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>30033404</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>30033404-2026,AP,VW Group,VW426-DP,Lamination,260033,M,Equipment</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Gong Shengchao_龚胜超(ugons034)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Huang Linjian_黄琳健(uhual254)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Phase 4 Manufacturing Development</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30033404</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>260033</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>VW Group,VW426-DP,Lamination</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>30035089</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>30035089-2026,AP,SAIC-GM,E2LB-2-IP, Automation, 260129, M,Equipment</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Zou Chengcheng_邹成成(uzouc016)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Wang Xiaoyu03_王晓宇(uwanx1357)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Phase 4 Manufacturing Development</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-06-13</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>30035089</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>260129</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>SAIC-GM,E2LB-2-IP, Automation</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" t="s">
+        <v>24</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/yanfeng/项目信息表/发运前检查计划.xlsx
+++ b/yanfeng/项目信息表/发运前检查计划.xlsx
@@ -1,112 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
-  <si>
-    <t>Project ID</t>
-  </si>
-  <si>
-    <t>Project Name</t>
-  </si>
-  <si>
-    <t>EBP Leader</t>
-  </si>
-  <si>
-    <t>Product Engineer</t>
-  </si>
-  <si>
-    <t>Project State</t>
-  </si>
-  <si>
-    <t>Phase 2 Gate Exit-DVR</t>
-  </si>
-  <si>
-    <t>Phase 3 Gate Exit-FPR</t>
-  </si>
-  <si>
-    <t>Phase 4 Gate Exit-CPA</t>
-  </si>
-  <si>
-    <t>项目号</t>
-  </si>
-  <si>
-    <t>工作令号</t>
-  </si>
-  <si>
-    <t>项目名</t>
-  </si>
-  <si>
-    <t>phase 2 score</t>
-  </si>
-  <si>
-    <t>phase 3 score</t>
-  </si>
-  <si>
-    <t>Phase 4 score</t>
-  </si>
-  <si>
-    <t>30034623</t>
-  </si>
-  <si>
-    <t>30034623-2026,AP,BYD,Glue,260103,M,Equipment</t>
-  </si>
-  <si>
-    <t>Shang Bing_尚兵(ushab007)</t>
-  </si>
-  <si>
-    <t>Chen Jie04_陈洁(uchej018)</t>
-  </si>
-  <si>
-    <t>Phase 4 Manufacturing Development</t>
-  </si>
-  <si>
-    <t>2026-05-22</t>
-  </si>
-  <si>
-    <t>2026-05-30</t>
-  </si>
-  <si>
-    <t>2026-06-20</t>
-  </si>
-  <si>
-    <t>260103</t>
-  </si>
-  <si>
-    <t>BYD,Glue</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -125,13 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -419,96 +408,87 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M2" t="s">
-        <v>24</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Project ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Project Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>EBP Leader</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Product Engineer</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Project State</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Phase 2 Gate Exit-DVR</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Phase 3 Gate Exit-FPR</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Phase 4 Gate Exit-CPA</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>项目号</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>工作令号</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>项目名</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>phase 2 score</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>phase 3 score</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Phase 4 score</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/yanfeng/项目信息表/发运前检查计划.xlsx
+++ b/yanfeng/项目信息表/发运前检查计划.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,6 +487,658 @@
           <t>Phase 4 score</t>
         </is>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>30032706</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>30032706-2025,AP,SERES Motors,A15-mirror, assy, 260006, 15T,Equipment</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Wang Baowei_王保卫(uwanb363)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Wang Wanfang_王万芳(uwanw356)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>30032706</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>260006</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>SERES Motors,A15-mirror, assy</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>30033723</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>30033723-2026,AP,VW Group,VW426 PAB Chute Cell CI,260042,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Wei Shaoguan_韦少官(uweis086)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>30033723</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>260042</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>VW Group,VW426 PAB Chute Cell CI</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>30034473</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>30034473-2026,AP,SERES Motors,F2N-light,260081,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Chen Jiarong_陈佳荣(uchej731)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Hao Xiuxia_郝秀霞(uhaox031)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>30034473</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>260081</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>SERES Motors,F2N-light</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>30033407</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>30033407-2026,AP,Huawei Anhui,F05/F03 CNSL,Assembly,260036,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Meng Zibing_孟子冰(umenz002)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>30033407</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>260036</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Huawei Anhui,F05/F03 CNSL,Assembly</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>30033405</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>30033405-2026,AP,Huawei Anhui,F05 IP,Assembly,260038,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Meng Zibing_孟子冰(umenz002)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>30033405</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>260038</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Huawei Anhui,F05 IP,Assembly</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>30033376</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>30033376-2026,AP,Huawei Anhui,F05&amp;F03,Assembly,260031,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Meng Zibing_孟子冰(umenz002)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>30033376</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>260031</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Huawei Anhui,F05&amp;F03,Assembly</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>30033375</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>30033375-2026,AP,Huawei Anhui,F05&amp;F03,Assembly,260032，T,Equipment</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Meng Zibing_孟子冰(umenz002)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>30033375</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>260032</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Huawei Anhui,F05&amp;F03,Assembly</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>30033373</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>30033373-2026,AP,Huawei Anhui,F03F05,Assembly,260030,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Meng Zibing_孟子冰(umenz002)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>30033373</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>260030</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Huawei Anhui,F03F05,Assembly</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>30035325</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>30035325-2026,AP,SERES Motors,遮阳板,1200压机,260145,1M,Equipment</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Meng Zibing_孟子冰(umenz002)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>30035325</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>260145</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>SERES Motors遮阳板1200压机</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>30034299</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>P780 2050 单工位压机</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Wang Xiang02_王翔(uwanx029)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>30034299</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>260077</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>P780 2050 单工位压机</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/yanfeng/项目信息表/发运前检查计划.xlsx
+++ b/yanfeng/项目信息表/发运前检查计划.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,7 +511,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Phase 5 Production Delivery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Phase 5 Production Delivery</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -711,7 +711,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Phase 5 Production Delivery</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -775,7 +775,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Phase 5 Production Delivery</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -839,7 +839,7 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Phase 5 Production Delivery</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -903,7 +903,7 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Phase 5 Production Delivery</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -967,7 +967,7 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Phase 5 Production Delivery</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1031,7 +1031,7 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Phase 5 Production Delivery</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1139,6 +1139,74 @@
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>30033911</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>30033911-2026,NA,Stellantis,WL-DP,laminnation,260060,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Wang Xiang02_王翔(uwanx029)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Jin Yulong01_金宇隆(ujiny132)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Phase 1 Quotation</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>30033911</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>260060</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>StellantisWL-DPlaminnation</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/yanfeng/项目信息表/发运前检查计划.xlsx
+++ b/yanfeng/项目信息表/发运前检查计划.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -627,57 +627,57 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>30034473</t>
+          <t>30034168</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30034473-2026,AP,SERES Motors,F2N-light,260081,M,Equipment</t>
+          <t>30034168-2026,AP,SVW,A-SUV-mirror,assembly,260008,15T,Equipment</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chen Jiarong_陈佳荣(uchej731)</t>
+          <t>Wang Baowei_王保卫(uwanb363)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Hao Xiuxia_郝秀霞(uhaox031)</t>
+          <t>Zhou Liwen_周理文(uzhol008)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Phase 5 Production Delivery</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30034473</t>
+          <t>30034168</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>260081</t>
+          <t>260008</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>SERES Motors,F2N-light</t>
+          <t>SVW,A-SUV-mirror,assembly</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -695,53 +695,57 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>30033407</t>
+          <t>30034171</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30033407-2026,AP,Huawei Anhui,F05/F03 CNSL,Assembly,260036,M,Equipment</t>
+          <t>30034171-2026,AP,Jianghuai,JHC-sun visor,assy, 260074, NT,Equipment</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Meng Zibing_孟子冰(umenz002)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Wang Baowei_王保卫(uwanb363)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Chen Zhibin01_陈志斌(uchez368)</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Phase 5 Production Delivery</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30033407</t>
+          <t>30034171</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>260036</t>
+          <t>260074</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Huawei Anhui,F05/F03 CNSL,Assembly</t>
+          <t>Jianghuai,JHC-sun visor,assy</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -759,53 +763,57 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>30033405</t>
+          <t>30034480</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>30033405-2026,AP,Huawei Anhui,F05 IP,Assembly,260038,M,Equipment</t>
+          <t>30034480-2028,AP,Toyota,780B,Spraying,260086,T,Equipment</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Meng Zibing_孟子冰(umenz002)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Kan Chengben_阚城奔(ukanc012)</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Phase 5 Production Delivery</t>
+          <t>Phase 2 Concept Definition</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>30033405</t>
+          <t>30034480</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>260038</t>
+          <t>260086</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Huawei Anhui,F05 IP,Assembly</t>
+          <t>Toyota,780B,Spraying</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -823,53 +831,57 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>30033376</t>
+          <t>30034479</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>30033376-2026,AP,Huawei Anhui,F05&amp;F03,Assembly,260031,T,Equipment</t>
+          <t>30034479-2027,AP,Toyota,780B,Spraying,260085,M,Equipment</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Meng Zibing_孟子冰(umenz002)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Chen Jie04_陈洁(uchej018)</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Phase 5 Production Delivery</t>
+          <t>Phase 3 Design Feasibility</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>30033376</t>
+          <t>30034479</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>260031</t>
+          <t>260085</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Huawei Anhui,F05&amp;F03,Assembly</t>
+          <t>Toyota,780B,Spraying</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -887,53 +899,57 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>30033375</t>
+          <t>30034746</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>30033375-2026,AP,Huawei Anhui,F05&amp;F03,Assembly,260032，T,Equipment</t>
+          <t>30034746-2026,AP,Huawei Anhui,X90-DP,260115,glue spray,M,Equipment</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Meng Zibing_孟子冰(umenz002)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Shang Bing_尚兵(ushab007)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Cheng Debao_程德宝(uched025)</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Phase 5 Production Delivery</t>
+          <t>Phase 4 Manufacturing Development</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>30033375</t>
+          <t>30034746</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>260032</t>
+          <t>260115</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Huawei Anhui,F05&amp;F03,Assembly</t>
+          <t>Huawei Anhui,X90-DP</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -951,12 +967,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>30033373</t>
+          <t>30033407</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>30033373-2026,AP,Huawei Anhui,F03F05,Assembly,260030,T,Equipment</t>
+          <t>30033407-2026,AP,Huawei Anhui,F05/F03 CNSL,Assembly,260036,M,Equipment</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -977,7 +993,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -987,17 +1003,17 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>30033373</t>
+          <t>30033407</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>260030</t>
+          <t>260036</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Huawei Anhui,F03F05,Assembly</t>
+          <t>Huawei Anhui,F05/F03 CNSL,Assembly</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1015,12 +1031,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>30035325</t>
+          <t>30033405</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>30035325-2026,AP,SERES Motors,遮阳板,1200压机,260145,1M,Equipment</t>
+          <t>30033405-2026,AP,Huawei Anhui,F05 IP,Assembly,260038,M,Equipment</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1036,12 +1052,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1051,17 +1067,17 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>30035325</t>
+          <t>30033405</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>260145</t>
+          <t>260038</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>SERES Motors遮阳板1200压机</t>
+          <t>Huawei Anhui,F05 IP,Assembly</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1079,53 +1095,53 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>30034299</t>
+          <t>30033376</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>P780 2050 单工位压机</t>
+          <t>30033376-2026,AP,Huawei Anhui,F05&amp;F03,Assembly,260031,T,Equipment</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wang Xiang02_王翔(uwanx029)</t>
+          <t>Meng Zibing_孟子冰(umenz002)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Phase 4 Manufacturing Development</t>
+          <t>Phase 5 Production Delivery</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>30034299</t>
+          <t>30033376</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>260077</t>
+          <t>260031</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>P780 2050 单工位压机</t>
+          <t>Huawei Anhui,F05&amp;F03,Assembly</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1143,70 +1159,462 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>30033375</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>30033375-2026,AP,Huawei Anhui,F05&amp;F03,Assembly,260032，T,Equipment</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Meng Zibing_孟子冰(umenz002)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Phase 5 Production Delivery</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>30033375</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>260032</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Huawei Anhui,F05&amp;F03,Assembly</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>30033373</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>30033373-2026,AP,Huawei Anhui,F03F05,Assembly,260030,T,Equipment</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Meng Zibing_孟子冰(umenz002)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Phase 5 Production Delivery</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>30033373</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>260030</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Huawei Anhui,F03F05,Assembly</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>30035325</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>30035325-2026,AP,SERES Motors,遮阳板,1200压机,260145,1M,Equipment</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Meng Zibing_孟子冰(umenz002)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Phase 5 Production Delivery</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>30035325</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>260145</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>SERES Motors遮阳板1200压机</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>30034299</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>P780 2050 单工位压机</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Wang Xiang02_王翔(uwanx029)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Phase 4 Manufacturing Development</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>30034299</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>260077</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>P780 2050 单工位压机</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>30033911</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>30033911-2026,NA,Stellantis,WL-DP,laminnation,260060,T,Equipment</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Wang Xiang02_王翔(uwanx029)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Jin Yulong01_金宇隆(ujiny132)</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Phase 1 Quotation</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>30033911</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>260060</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>StellantisWL-DPlaminnation</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>30034479B/C/D</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>30034479-2027,AP,Toyota,780B,Spraying,260085,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Gong Shengchao_龚胜超(ugons034)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Chen Jie04_陈洁(uchej018)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Phase 2 Concept Definition</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>30034479</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>260085</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Toyota,780B,Spraying</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>30034473_</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>30034473-2026,AP,SERES Motors,F2N-light,260082,M,Equipment</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Chen Jiarong_陈佳荣(uchej731)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Hao Xiuxia_郝秀霞(uhaox031)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Phase 5 Production Delivery</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>30034473</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>260082</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>SERES Motors,F2N-light</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
